--- a/data/gravel/Chiru Divider 2025.xlsx
+++ b/data/gravel/Chiru Divider 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC56C86C-627B-2649-BAA0-5BACB3C9DC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF27E4D9-80D6-254F-8CBF-F30C250CDADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34980" yWindow="-23900" windowWidth="26260" windowHeight="15260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10800" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="101">
   <si>
     <t>brand</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>a8:f30</t>
+  </si>
+  <si>
+    <t>https://www.chirubikes.com/wp-content/uploads/2022/10/chiru-divider-aventure-cover-1.jpg</t>
   </si>
 </sst>
 </file>
@@ -705,6 +708,11 @@
         <v>95</v>
       </c>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+    </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Chiru Divider 2025.xlsx
+++ b/data/gravel/Chiru Divider 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF27E4D9-80D6-254F-8CBF-F30C250CDADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D292EADE-CF1A-2D4E-93CD-5AFB0638D7DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10800" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="103">
   <si>
     <t>brand</t>
   </si>
@@ -323,6 +323,12 @@
   </si>
   <si>
     <t>https://www.chirubikes.com/wp-content/uploads/2022/10/chiru-divider-aventure-cover-1.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Paris, France</t>
   </si>
 </sst>
 </file>
@@ -662,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1388,6 +1394,14 @@
         <v>91</v>
       </c>
     </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>101</v>
+      </c>
+      <c r="B71" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Chiru Divider 2025.xlsx
+++ b/data/gravel/Chiru Divider 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D292EADE-CF1A-2D4E-93CD-5AFB0638D7DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EBB5B8-CF2E-6C45-95CE-C8144C0DA857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -329,6 +329,24 @@
   </si>
   <si>
     <t>Paris, France</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -668,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1225,180 +1243,210 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>61</v>
-      </c>
-      <c r="B49">
-        <v>27.2</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>63</v>
-      </c>
-      <c r="B51">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>66</v>
-      </c>
-      <c r="B54">
-        <v>160</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>61</v>
+      </c>
+      <c r="B55">
+        <v>27.2</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>68</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>93</v>
+        <v>63</v>
+      </c>
+      <c r="B57">
+        <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>70</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>73</v>
-      </c>
-      <c r="B61">
-        <v>1</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>74</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
+        <v>68</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>77</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>78</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>90</v>
+        <v>72</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B67">
-        <v>2725</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>98</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>80</v>
+        <v>74</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73">
+        <v>2725</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>101</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B77" t="s">
         <v>102</v>
       </c>
     </row>

--- a/data/gravel/Chiru Divider 2025.xlsx
+++ b/data/gravel/Chiru Divider 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EBB5B8-CF2E-6C45-95CE-C8144C0DA857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D9EC71-AECD-EA41-AD54-B6C7ADF828E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4980" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -319,9 +319,6 @@
     <t>frame only</t>
   </si>
   <si>
-    <t>a8:f30</t>
-  </si>
-  <si>
     <t>https://www.chirubikes.com/wp-content/uploads/2022/10/chiru-divider-aventure-cover-1.jpg</t>
   </si>
   <si>
@@ -347,6 +344,18 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:f32</t>
+  </si>
+  <si>
+    <t>100-120</t>
   </si>
 </sst>
 </file>
@@ -686,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -734,7 +743,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -742,7 +751,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1006,400 +1015,418 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>35</v>
+      <c r="A21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" t="s">
-        <v>36</v>
+      <c r="A22" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+      <c r="B25" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26">
-        <v>700</v>
-      </c>
-      <c r="D26">
-        <v>700</v>
-      </c>
-      <c r="E26">
-        <v>700</v>
-      </c>
-      <c r="F26">
-        <v>700</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27">
-        <v>2.4</v>
-      </c>
-      <c r="D27">
-        <v>2.4</v>
-      </c>
-      <c r="E27">
-        <v>2.4</v>
-      </c>
-      <c r="F27">
-        <v>2.4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C28">
-        <v>2.8</v>
+        <v>700</v>
       </c>
       <c r="D28">
-        <v>2.8</v>
+        <v>700</v>
       </c>
       <c r="E28">
-        <v>2.8</v>
+        <v>700</v>
       </c>
       <c r="F28">
-        <v>2.8</v>
+        <v>700</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="B29" t="s">
+        <v>41</v>
       </c>
       <c r="C29">
-        <v>163</v>
+        <v>2.4</v>
       </c>
       <c r="D29">
-        <v>173</v>
+        <v>2.4</v>
       </c>
       <c r="E29">
-        <v>180</v>
+        <v>2.4</v>
       </c>
       <c r="F29">
-        <v>190</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="B30" t="s">
+        <v>42</v>
       </c>
       <c r="C30">
+        <v>2.8</v>
+      </c>
+      <c r="D30">
+        <v>2.8</v>
+      </c>
+      <c r="E30">
+        <v>2.8</v>
+      </c>
+      <c r="F30">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31">
+        <v>163</v>
+      </c>
+      <c r="D31">
         <v>173</v>
       </c>
-      <c r="D30">
+      <c r="E31">
         <v>180</v>
       </c>
-      <c r="E30">
+      <c r="F31">
         <v>190</v>
-      </c>
-      <c r="F30">
-        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>83</v>
-      </c>
-      <c r="B33" t="s">
-        <v>84</v>
+        <v>44</v>
+      </c>
+      <c r="C32">
+        <v>173</v>
+      </c>
+      <c r="D32">
+        <v>180</v>
+      </c>
+      <c r="E32">
+        <v>190</v>
+      </c>
+      <c r="F32">
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
+      </c>
+      <c r="B37" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="B38" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39">
-        <v>2.8</v>
+        <v>49</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>52</v>
-      </c>
-      <c r="B40">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B41">
-        <v>100</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="B42">
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>53</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>57</v>
-      </c>
-      <c r="B45">
-        <v>148</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>58</v>
-      </c>
-      <c r="B46">
-        <v>110</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>103</v>
+        <v>57</v>
+      </c>
+      <c r="B47">
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>104</v>
+        <v>58</v>
+      </c>
+      <c r="B48">
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55">
-        <v>27.2</v>
+        <v>59</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B57">
-        <v>34</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>63</v>
+      </c>
+      <c r="B59">
+        <v>34</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>66</v>
-      </c>
-      <c r="B60">
-        <v>160</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>92</v>
+        <v>66</v>
+      </c>
+      <c r="B62">
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>71</v>
+        <v>69</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>72</v>
-      </c>
-      <c r="B66">
-        <v>2</v>
+        <v>70</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>73</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
+        <v>71</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>90</v>
+        <v>73</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>90</v>
@@ -1407,7 +1434,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>90</v>
@@ -1415,39 +1442,55 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>79</v>
-      </c>
-      <c r="B73">
-        <v>2725</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>98</v>
+        <v>77</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="B75">
+        <v>2725</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>82</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>100</v>
+      </c>
+      <c r="B79" t="s">
         <v>101</v>
-      </c>
-      <c r="B77" t="s">
-        <v>102</v>
       </c>
     </row>
   </sheetData>
